--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/02. Trả bảo hành/TBH_DLSea_250326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/02. Trả bảo hành/TBH_DLSea_250326.xlsx
@@ -15,14 +15,14 @@
     <sheet name="P.TraBaoHanh" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -111,70 +111,85 @@
     <t>Trần Văn Hậu</t>
   </si>
   <si>
-    <t>Khách hàng/ người đại diện: Đại lý Thành Tâm Nha Trang</t>
-  </si>
-  <si>
-    <t>005694061006115</t>
-  </si>
-  <si>
-    <t>006011074346818</t>
-  </si>
-  <si>
-    <t>003200D952</t>
-  </si>
-  <si>
     <t>Sim</t>
   </si>
   <si>
-    <t>ESIM: 01388295854</t>
-  </si>
-  <si>
-    <t>Hết hạn dịch vụ</t>
-  </si>
-  <si>
-    <t>Lỗi GPS</t>
-  </si>
-  <si>
-    <t>Thay module GPS</t>
-  </si>
-  <si>
-    <t>Không chốt GPS</t>
-  </si>
-  <si>
-    <t>Thay IC GPS</t>
-  </si>
-  <si>
-    <t>Lỗi hồng ngoại</t>
-  </si>
-  <si>
-    <t>Thay IC hồng ngoại</t>
-  </si>
-  <si>
-    <t>VNSH02</t>
-  </si>
-  <si>
-    <t>Hà Nội, ngày 20 tháng 03 năm 2026</t>
-  </si>
-  <si>
-    <t>006011071686166</t>
-  </si>
-  <si>
-    <t>KH báo không sửa</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>005694061010851</t>
-  </si>
-  <si>
-    <t>ESIM: 01388295801</t>
-  </si>
-  <si>
     <t>Không nhận sim</t>
   </si>
   <si>
-    <t>Thay IC esim</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>005105051211045</t>
+  </si>
+  <si>
+    <t>005185070132405</t>
+  </si>
+  <si>
+    <t>005185070122257</t>
+  </si>
+  <si>
+    <t>005185070122992</t>
+  </si>
+  <si>
+    <t>005185070148369</t>
+  </si>
+  <si>
+    <t>005185070126506</t>
+  </si>
+  <si>
+    <t>005694061490806</t>
+  </si>
+  <si>
+    <t>005694061428186</t>
+  </si>
+  <si>
+    <t>005694061421975</t>
+  </si>
+  <si>
+    <t>005694061006438</t>
+  </si>
+  <si>
+    <t>Hết hạn DV</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 25 tháng 03 năm 2026</t>
+  </si>
+  <si>
+    <t>Khách hàng/ người đại diện: Đại lý SEA</t>
+  </si>
+  <si>
+    <t>Mất giao tiếp</t>
+  </si>
+  <si>
+    <t>Nguồn chập chờn</t>
+  </si>
+  <si>
+    <t>Hay mất GSM</t>
+  </si>
+  <si>
+    <t>Chập nguồn</t>
+  </si>
+  <si>
+    <t>Xử lý phần mềm</t>
+  </si>
+  <si>
+    <t>Xử lý phần cứng + phần mềm</t>
   </si>
 </sst>
 </file>
@@ -572,6 +587,39 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -596,40 +644,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -992,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="5" customWidth="1"/>
@@ -1010,77 +1025,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="51" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="52" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="54"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="55" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="49"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="58" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="60"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="A6" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="25"/>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
@@ -1088,12 +1103,12 @@
       <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="25"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
@@ -1101,12 +1116,12 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="25"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
@@ -1114,12 +1129,12 @@
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="25"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
@@ -1164,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="41" t="s">
@@ -1172,10 +1187,10 @@
       </c>
       <c r="F11" s="41"/>
       <c r="G11" s="41" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="7"/>
@@ -1188,20 +1203,18 @@
         <v>21</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D12" s="36"/>
       <c r="E12" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>34</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F12" s="41"/>
       <c r="G12" s="41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H12" s="41" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="7"/>
@@ -1214,20 +1227,18 @@
         <v>21</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D13" s="36"/>
       <c r="E13" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>48</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F13" s="61"/>
       <c r="G13" s="41" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I13" s="36"/>
       <c r="J13" s="7"/>
@@ -1240,216 +1251,336 @@
         <v>21</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E14" s="41" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I14" s="36"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D15" s="36"/>
       <c r="E15" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>35</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F15" s="34"/>
       <c r="G15" s="41" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I15" s="36"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="40"/>
+    <row r="16" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="36"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+    <row r="17" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="36"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="28"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+    <row r="18" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="36"/>
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="36"/>
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="36"/>
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="60"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="46" t="s">
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="47" t="s">
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="48" t="s">
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="48" t="s">
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="19"/>
-    </row>
-    <row r="28" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-    </row>
-    <row r="67" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
+    </row>
+    <row r="33" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+    </row>
+    <row r="72" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A16:H16"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <pageMargins left="0.70866141732283472" right="0.78740157480314965" top="0.98425196850393704" bottom="0.98425196850393704" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="1.4960629921259843" right="0.78740157480314965" top="0.59055118110236227" bottom="0.98425196850393704" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>